--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260626_211223.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260626_211223.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260626_211223.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260626_211223.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
